--- a/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,7 +673,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -689,7 +689,8 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1350,7 +1351,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1660,6 +1661,9 @@
   </si>
   <si>
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
@@ -2124,9 +2128,6 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2455,17 +2456,17 @@
   <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.96875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2474,28 +2475,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.3046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4780,7 +4781,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>206</v>
       </c>
@@ -4876,7 +4877,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -5502,7 +5503,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>248</v>
       </c>
@@ -5742,7 +5743,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>271</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>277</v>
       </c>
@@ -6464,7 +6465,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>290</v>
       </c>
@@ -6706,7 +6707,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>308</v>
       </c>
@@ -7190,7 +7191,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>344</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>381</v>
       </c>
@@ -9122,7 +9123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>408</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>449</v>
       </c>
@@ -9966,7 +9967,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>456</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>477</v>
       </c>
@@ -10330,7 +10331,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>485</v>
       </c>
@@ -10450,7 +10451,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>494</v>
       </c>
@@ -10572,7 +10573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>503</v>
       </c>
@@ -12085,9 +12086,11 @@
       <c r="X80" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Y80" s="2"/>
+      <c r="Y80" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12123,27 +12126,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12166,19 +12169,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12227,7 +12230,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12248,10 +12251,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12262,10 +12265,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12291,13 +12294,13 @@
         <v>261</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12326,10 +12329,10 @@
         <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12347,7 +12350,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12365,27 +12368,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12411,16 +12414,16 @@
         <v>261</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12449,7 +12452,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12467,7 +12470,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12488,10 +12491,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12502,10 +12505,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12528,16 +12531,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12587,7 +12590,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12605,27 +12608,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12648,16 +12651,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12707,7 +12710,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12725,27 +12728,27 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12768,19 +12771,19 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12829,7 +12832,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12841,7 +12844,7 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12850,10 +12853,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12864,10 +12867,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12982,10 +12985,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13102,14 +13105,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13131,10 +13134,10 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
@@ -13189,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13224,10 +13227,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13250,13 +13253,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13307,7 +13310,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13316,7 +13319,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13328,10 +13331,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13342,10 +13345,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13368,13 +13371,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13425,7 +13428,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13434,7 +13437,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13446,10 +13449,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13460,10 +13463,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13489,16 +13492,16 @@
         <v>261</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13526,10 +13529,10 @@
         <v>177</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13547,7 +13550,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13565,13 +13568,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13582,10 +13585,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13611,16 +13614,16 @@
         <v>261</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13648,10 +13651,10 @@
         <v>163</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13669,7 +13672,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13687,13 +13690,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13704,10 +13707,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13730,17 +13733,17 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13789,7 +13792,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13813,7 +13816,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13824,10 +13827,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13853,10 +13856,10 @@
         <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13907,7 +13910,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13928,10 +13931,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13942,10 +13945,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13968,16 +13971,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14027,7 +14030,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14048,10 +14051,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14062,10 +14065,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14088,16 +14091,16 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14147,7 +14150,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14168,10 +14171,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14180,12 +14183,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14208,19 +14211,19 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14269,7 +14272,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14281,7 +14284,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14290,10 +14293,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14304,10 +14307,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14422,10 +14425,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14542,14 +14545,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14571,10 +14574,10 @@
         <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>117</v>
@@ -14629,7 +14632,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14662,12 +14665,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14693,16 +14696,16 @@
         <v>261</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14751,7 +14754,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>93</v>
@@ -14769,7 +14772,7 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>354</v>
@@ -14784,12 +14787,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14812,16 +14815,16 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>441</v>
@@ -14849,13 +14852,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14873,7 +14876,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14882,7 +14885,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14891,7 +14894,7 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>446</v>
@@ -14906,12 +14909,12 @@
         <v>448</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14937,13 +14940,13 @@
         <v>261</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O104" t="s" s="2">
         <v>507</v>
@@ -14995,7 +14998,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15004,7 +15007,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15030,10 +15033,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15096,28 +15099,28 @@
         <v>155</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15135,19 +15138,19 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -15187,10 +15190,10 @@
         <v>678</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15260,10 +15263,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15274,12 +15277,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP106">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
